--- a/results/calibration_results_master.xlsx
+++ b/results/calibration_results_master.xlsx
@@ -1408,16 +1408,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0414273062484926</v>
+        <v>0.0391826856168453</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0501616478287627</v>
+        <v>0.0472977394363629</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7529309596178897</v>
+        <v>0.7640758431031986</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0922221920498468</v>
+        <v>0.091654400562028</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1456,16 +1456,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0373331835484226</v>
+        <v>0.0366356788447157</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0404301009535699</v>
+        <v>0.0401177829367202</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7599507888261687</v>
+        <v>0.7647271674627298</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0912712100033132</v>
+        <v>0.0910499760159712</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0583130526896114</v>
+        <v>0.0410023931705083</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0594891243064499</v>
+        <v>0.0509356945512108</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.8199079401611048</v>
+        <v>0.819620253164557</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0988138266975547</v>
+        <v>0.1002976195749488</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0544393612663388</v>
+        <v>0.0441436354249884</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0713713619601949</v>
+        <v>0.048201220049311</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.8164556962025317</v>
+        <v>0.8154200230149596</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.100324255635607</v>
+        <v>0.1004788745371115</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0234770833026795</v>
+        <v>0.0268204004991622</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0584313000951494</v>
+        <v>0.0465042852220081</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7046290951075191</v>
+        <v>0.7025364410448838</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1436529792216732</v>
+        <v>0.1446549727715895</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -2120,16 +2120,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0371789375207253</v>
+        <v>0.036756165053013</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.053045153375367</v>
+        <v>0.0482579440536738</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7030054841968538</v>
+        <v>0.7048816568047337</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1447752259739189</v>
+        <v>0.1445917528181202</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -2391,16 +2391,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0388074343894967</v>
+        <v>0.0508745672310342</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0494656320108045</v>
+        <v>0.0509293888243708</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.7811554151862088</v>
+        <v>0.7826556125806027</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1797068641076777</v>
+        <v>0.1791193313779527</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -2439,16 +2439,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0551737354412495</v>
+        <v>0.0478811463523285</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0551157521427839</v>
+        <v>0.0550141025514605</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.7788393209632847</v>
+        <v>0.7778918278720885</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.1826064795796357</v>
+        <v>0.1828052454042991</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -2736,16 +2736,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0303326041698455</v>
+        <v>0.0293322855234146</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0582579566240311</v>
+        <v>0.0560587364435196</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.6422401198042224</v>
+        <v>0.6337478997735408</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.2068452232914008</v>
+        <v>0.2079118232056215</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -2784,16 +2784,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.043037573225953</v>
+        <v>0.0675958988634682</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.085196952952394</v>
+        <v>0.0682452025709889</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.6346245160347725</v>
+        <v>0.6287438819490101</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.2092699348741287</v>
+        <v>0.2107795645358461</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.06629721902310839</v>
+        <v>0.0610197532922029</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0731964475661516</v>
+        <v>0.09650752581655971</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.7445798727213891</v>
+        <v>0.7458742314744904</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1950470785674399</v>
+        <v>0.1947175172768888</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -3103,16 +3103,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0741705605072811</v>
+        <v>0.0706533397074416</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0938264417496134</v>
+        <v>0.0637843940173554</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.73929457447956</v>
+        <v>0.7373530363499083</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.1973232706142787</v>
+        <v>0.1971892652814414</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -3400,16 +3400,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0477382720708847</v>
+        <v>0.060169622041285</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0410459154844284</v>
+        <v>0.0587407152280211</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.84245826709062</v>
+        <v>0.8408684419713832</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1593429496603514</v>
+        <v>0.1601246446390918</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -3448,16 +3448,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.05311773230252</v>
+        <v>0.0503419091019339</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0538658790639865</v>
+        <v>0.0612237164300177</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.8338135930047694</v>
+        <v>0.8337307896131425</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1624713302642987</v>
+        <v>0.1626005650131539</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -3719,16 +3719,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0642934729196131</v>
+        <v>0.0629102133288979</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0672390531934797</v>
+        <v>0.075398990444839</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.7620559704096587</v>
+        <v>0.7282085281596762</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1800036825960321</v>
+        <v>0.1910759499467099</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -3767,16 +3767,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0773802743585205</v>
+        <v>0.08681627283809</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0832186683469736</v>
+        <v>0.08616621487158831</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.7193628306232116</v>
+        <v>0.7067834461581408</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.2006647812318973</v>
+        <v>0.2066271560528332</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -4064,16 +4064,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0530126131051219</v>
+        <v>0.0620477101691067</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0655327024930156</v>
+        <v>0.0708762660212815</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.8329767295284536</v>
+        <v>0.8377038032210447</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1643438469670865</v>
+        <v>0.1633380640559222</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -4112,16 +4112,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0672173624858665</v>
+        <v>0.0678958133778107</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0735274564543615</v>
+        <v>0.073954757100471</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.8356636977326632</v>
+        <v>0.8355807666152493</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1638630026167679</v>
+        <v>0.1640010055809327</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -4383,16 +4383,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0599342763237655</v>
+        <v>0.0581201290525496</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0476276184730231</v>
+        <v>0.0681364729441702</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.799400074990626</v>
+        <v>0.7987604490615144</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1439245914963808</v>
+        <v>0.1471212720920504</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -4431,16 +4431,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0607559235325155</v>
+        <v>0.060693861204388</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0561883278728386</v>
+        <v>0.0518203402546</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.8033701669644235</v>
+        <v>0.8028628774344384</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.1471075545473904</v>
+        <v>0.1476153836576534</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -4728,16 +4728,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0693080826774239</v>
+        <v>0.0683666338324546</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0640767282024025</v>
+        <v>0.0787226635813713</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.794808201058201</v>
+        <v>0.7819822373393802</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.138849684087251</v>
+        <v>0.1438549670349855</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -4776,16 +4776,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0539624282673602</v>
+        <v>0.0457087304183394</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0872338009946871</v>
+        <v>0.0698432642811654</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7684476568405141</v>
+        <v>0.7713293650793651</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1421961134863753</v>
+        <v>0.1420311404618216</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -5047,16 +5047,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0833563949167728</v>
+        <v>0.079640741944313</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.09814904376864431</v>
+        <v>0.06675517082214349</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.7890625</v>
+        <v>0.786047149122807</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1531753090910079</v>
+        <v>0.1522054591253214</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -5095,16 +5095,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0995884422859859</v>
+        <v>0.1029983350152124</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.1129910840653996</v>
+        <v>0.1178951459657736</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.7582236842105263</v>
+        <v>0.7582236842105262</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.1544681291608227</v>
+        <v>0.1548432009541706</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -5392,16 +5392,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0697438307702541</v>
+        <v>0.0702362337708473</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0951195200383663</v>
+        <v>0.09526135188341139</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.6416087078051267</v>
+        <v>0.6452424406846545</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.2317422742093862</v>
+        <v>0.2308868159950006</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.070485540669318</v>
+        <v>0.0576318766674033</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0776557364810911</v>
+        <v>0.113556592789863</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.6370953156086092</v>
+        <v>0.6371610845295055</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.2326304127804471</v>
+        <v>0.2321490955087143</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -5711,16 +5711,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0999967803806066</v>
+        <v>0.1466089357435703</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.127762721851468</v>
+        <v>0.1248133246600628</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.6996281780725554</v>
+        <v>0.6973168525776303</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.2193190038540945</v>
+        <v>0.2179411001471734</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -5759,16 +5759,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0788453392042833</v>
+        <v>0.0866259112146021</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.1482285052203004</v>
+        <v>0.1136475044703896</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.7065621545573308</v>
+        <v>0.7031454125213547</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.2168679143062122</v>
+        <v>0.2169136219797841</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -6056,16 +6056,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0260600510798394</v>
+        <v>0.0341114686783403</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0303687149249017</v>
+        <v>0.0326657267417758</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.8366788766788767</v>
+        <v>0.8274969474969475</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0678570668880064</v>
+        <v>0.06841858290559499</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -6104,16 +6104,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0353072762232562</v>
+        <v>0.0328300596575699</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.028573757152288</v>
+        <v>0.0203230087741482</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.8375579975579975</v>
+        <v>0.8360439560439561</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0681968408259913</v>
+        <v>0.06834949014000891</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -6375,16 +6375,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0197417381592094</v>
+        <v>0.0237031287234276</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0630647279508412</v>
+        <v>0.0680168697517365</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.7129724208375894</v>
+        <v>0.7060776302349336</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0920511794890066</v>
+        <v>0.0919566707280798</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -6423,16 +6423,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.008407225502152</v>
+        <v>0.0085364383743496</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.06590136204560661</v>
+        <v>0.0475818804657588</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.5257916241062308</v>
+        <v>0.526046986721144</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.0977322846840494</v>
+        <v>0.0976951118698821</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -6720,16 +6720,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0190104336244985</v>
+        <v>0.0203513838630169</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0311087451316416</v>
+        <v>0.0292766467407345</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.7303157093952074</v>
+        <v>0.7371624191707874</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0411096069592869</v>
+        <v>0.0409190969283196</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -6768,16 +6768,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0204670697028163</v>
+        <v>0.020085814597341</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0265385653757316</v>
+        <v>0.0253431584352759</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7384937238493723</v>
+        <v>0.7370673259794599</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0417855434375025</v>
+        <v>0.041785784144644</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -7039,16 +7039,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0208779350668191</v>
+        <v>0.0079179805493913</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0313366661220789</v>
+        <v>0.0359506660164333</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.7838541666666666</v>
+        <v>0.6809895833333334</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0364641793902275</v>
+        <v>0.0372502280520649</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -7087,16 +7087,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0044664794505417</v>
+        <v>0.0047870041851321</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0437422122210251</v>
+        <v>0.044233617933957</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.6647135416666666</v>
+        <v>0.6536458333333334</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.0381078883523488</v>
+        <v>0.0382138886525495</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -7384,16 +7384,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.07970090188086031</v>
+        <v>0.0468183397948741</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0829537709206343</v>
+        <v>0.0447280292809009</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.6869093139023157</v>
+        <v>0.7004094221196163</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.2012851297457719</v>
+        <v>0.1985484469333324</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -7432,16 +7432,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0521689957563656</v>
+        <v>0.0592273545790596</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0670718376626256</v>
+        <v>0.0597775249170785</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.7035116513960031</v>
+        <v>0.7080748142269677</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1950084866893705</v>
+        <v>0.1946969446585122</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -7703,16 +7703,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.1012242549657821</v>
+        <v>0.1358867061138153</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0997575369477272</v>
+        <v>0.1394325536489486</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.7599291957074897</v>
+        <v>0.7630268835048125</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1856589764457864</v>
+        <v>0.1851498935135805</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -7751,16 +7751,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0840136812430803</v>
+        <v>0.08804219851737891</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.1044554283762782</v>
+        <v>0.11402422638742</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.7569421396172142</v>
+        <v>0.7588228786370174</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.1860506845216237</v>
+        <v>0.1856269967191408</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -8048,16 +8048,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0002055465642479</v>
+        <v>0.0002762173963128</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0110544629067298</v>
+        <v>0.0102832866431563</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.595766129032258</v>
+        <v>0.6617943548387096</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.0079335527989073</v>
+        <v>0.007913245330409199</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -8096,16 +8096,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0005746748163085</v>
+        <v>0.0005804956777396</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0131362795449365</v>
+        <v>0.0131390633456571</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.4248991935483871</v>
+        <v>0.4223790322580645</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0079429239996589</v>
+        <v>0.0079429398750417</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -8367,16 +8367,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0031846814224627</v>
+        <v>0.003331033450122</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0107612993748989</v>
+        <v>0.0110316206445349</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.9045226130653268</v>
+        <v>0.9246231155778896</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0049304604007795</v>
+        <v>0.004926761724516</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -8415,16 +8415,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.00285456811362</v>
+        <v>0.002851811630668</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0110388510243721</v>
+        <v>0.0110376916628278</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0.7688442211055276</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.0049640651267491</v>
+        <v>0.0049638179474554</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -8712,16 +8712,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0797823336652734</v>
+        <v>0.0564491748809814</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0845849592238664</v>
+        <v>0.1028657380830157</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.6426992314980524</v>
+        <v>0.6522791872828718</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1909877173957252</v>
+        <v>0.1899148505707685</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -8760,16 +8760,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0088700498393788</v>
+        <v>0.008683075327286301</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.099317354764587</v>
+        <v>0.09944458685460961</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.5085798505105801</v>
+        <v>0.5206863880408463</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1941779525474872</v>
+        <v>0.1942508168171545</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -9031,16 +9031,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0663138335105031</v>
+        <v>0.0569414038583636</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.08016392693854869</v>
+        <v>0.0807035791501403</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.5756595636732623</v>
+        <v>0.6068619989852866</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1942977185809413</v>
+        <v>0.1919447720200565</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -9079,16 +9079,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0183487157798349</v>
+        <v>0.0716176666802549</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.1041933760173994</v>
+        <v>0.0941695692221126</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.6021689497716896</v>
+        <v>0.6253805175038052</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.195548657464131</v>
+        <v>0.1949381057278232</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -9376,16 +9376,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.044602942764759</v>
+        <v>0.0409236796974873</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0661013222336769</v>
+        <v>0.0528613575816416</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.6893400716930129</v>
+        <v>0.6910834263775438</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.1855853661404867</v>
+        <v>0.1869267030177952</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -9424,16 +9424,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0517824057243972</v>
+        <v>0.057882151166305</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0454666756398896</v>
+        <v>0.0537903234560563</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.6906916612798966</v>
+        <v>0.6905545434957199</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.1855416536542819</v>
+        <v>0.1885566072289334</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -9695,16 +9695,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.07554483987390991</v>
+        <v>0.0988146635144948</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0524315456300973</v>
+        <v>0.101072022691369</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.8428413691571587</v>
+        <v>0.8265243528401423</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.1445291167400114</v>
+        <v>0.150189118132016</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -9743,16 +9743,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.07436075835952501</v>
+        <v>0.0645934361022398</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0658335538741658</v>
+        <v>0.0765615209951442</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.831186357502147</v>
+        <v>0.8293460925039873</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.1482498223664965</v>
+        <v>0.1497677627607748</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -10040,16 +10040,16 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0.0191789832455744</v>
+        <v>0.0169348890827508</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.0354046452214281</v>
+        <v>0.0364822698151286</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.641025641025641</v>
+        <v>0.6252465483234714</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>0.020697718558281</v>
+        <v>0.0199436581497105</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -10088,16 +10088,16 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0.0188953981072319</v>
+        <v>0.0195528363078007</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.0347526995121748</v>
+        <v>0.0345077535957687</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0.6390532544378698</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.0208107188032083</v>
+        <v>0.0205869240392087</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -10359,16 +10359,16 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>0.0021299556219039</v>
+        <v>0.0013724636805289</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.0204510105365845</v>
+        <v>0.0203892592579968</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.7441176470588236</v>
+        <v>0.7147058823529411</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.0116029909226244</v>
+        <v>0.0115973741692124</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -10407,16 +10407,16 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>0.0015056360352686</v>
+        <v>0.0015058123109828</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.0214591675211905</v>
+        <v>0.0214586836847313</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>0.3441176470588235</v>
+        <v>0.3470588235294117</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.0115155715525601</v>
+        <v>0.0115155400888486</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
